--- a/OTA.xlsx
+++ b/OTA.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="23040" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -33,12 +33,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="105">
   <si>
     <t>BUS NAME</t>
   </si>
   <si>
-    <t>number</t>
+    <t>box index</t>
+  </si>
+  <si>
+    <t>box channel index</t>
   </si>
   <si>
     <t>channel bus</t>
@@ -332,58 +335,19 @@
     <t>0x669</t>
   </si>
   <si>
-    <t>Signal Name</t>
-  </si>
-  <si>
     <t>Msg ID</t>
   </si>
   <si>
-    <t>Siganl Name1</t>
-  </si>
-  <si>
-    <t>Siganl Name2</t>
-  </si>
-  <si>
-    <t>Siganl Name3</t>
-  </si>
-  <si>
-    <t>Siganl Name4</t>
-  </si>
-  <si>
-    <t>LHMPWC1</t>
-  </si>
-  <si>
-    <t>0x0A5</t>
-  </si>
-  <si>
-    <t>ABM_CrashTyp</t>
-  </si>
-  <si>
-    <t>ABM_CrashTypSply</t>
-  </si>
-  <si>
-    <t>ABM_IMU_LateralAcceleration</t>
-  </si>
-  <si>
-    <t>ABM_IMU_LateralAccValid</t>
-  </si>
-  <si>
-    <t>LHMPWD2</t>
-  </si>
-  <si>
-    <t>0x0AD</t>
-  </si>
-  <si>
-    <t>LHMPWC2</t>
-  </si>
-  <si>
-    <t>0x0AE</t>
-  </si>
-  <si>
-    <t>LHMPWD3</t>
-  </si>
-  <si>
-    <t>0x0A4</t>
+    <t>Startbit</t>
+  </si>
+  <si>
+    <t>len</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>0x343</t>
   </si>
 </sst>
 </file>
@@ -1329,21 +1293,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="21.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="15.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="15.1111111111111" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="8" width="25.5555555555556" customWidth="1"/>
-    <col min="9" max="9" width="45.0925925925926" customWidth="1"/>
-    <col min="10" max="10" width="29.8055555555556" customWidth="1"/>
-    <col min="11" max="11" width="26.4074074074074" customWidth="1"/>
+    <col min="3" max="3" width="16.212962962963" customWidth="1"/>
+    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="15.1111111111111" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="12.75" customWidth="1"/>
+    <col min="8" max="9" width="25.5555555555556" customWidth="1"/>
+    <col min="10" max="10" width="45.0925925925926" customWidth="1"/>
+    <col min="11" max="11" width="29.8055555555556" customWidth="1"/>
+    <col min="12" max="12" width="26.4074074074074" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1374,25 +1339,31 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
       </c>
       <c r="C2" s="1">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
+      <c r="D2" s="1">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
@@ -1402,327 +1373,411 @@
       <c r="J2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="K2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
       </c>
       <c r="C3" s="1">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3" s="1">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1">
         <v>2</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="D4" s="1">
         <v>3</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="F4" s="1">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1">
+        <v>2</v>
+      </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="G5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
       </c>
       <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
         <v>8</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="1">
         <v>20</v>
       </c>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1" t="s">
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1" t="s">
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="1">
+        <v>37</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2</v>
       </c>
       <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1">
         <v>9</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>39</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="1">
+        <v>41</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
       </c>
       <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
         <v>4</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>43</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>44</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="1">
+        <v>45</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
       </c>
       <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
         <v>4</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="E11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="1">
         <v>2</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="I11" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
       </c>
       <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="E12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="1">
         <v>3</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
       </c>
       <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
         <v>4</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="E13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="1">
         <v>4</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
       </c>
       <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
         <v>4</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="E14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="1">
         <v>5</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1</v>
       </c>
       <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
         <v>4</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="1">
+      <c r="E15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="1">
         <v>6</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1</v>
       </c>
       <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
         <v>5</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>62</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>63</v>
@@ -1733,88 +1788,112 @@
       <c r="J16" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K16" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
       </c>
       <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1">
         <v>5</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="E17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="1">
         <v>2</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I17" s="1"/>
+      <c r="I17" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
       </c>
       <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
         <v>5</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="1">
+      <c r="E18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="1">
         <v>3</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I18" s="1"/>
+      <c r="I18" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1</v>
       </c>
       <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1">
         <v>5</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" s="1">
+      <c r="E19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="1">
         <v>4</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="1"/>
+      <c r="I19" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1</v>
       </c>
       <c r="C20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1">
         <v>7</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>77</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>78</v>
@@ -1825,66 +1904,84 @@
       <c r="J20" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1</v>
       </c>
       <c r="C21" s="1">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1">
         <v>7</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="E21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="1">
         <v>2</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I21" s="1"/>
+      <c r="I21" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1</v>
       </c>
       <c r="C22" s="1">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1">
         <v>7</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" s="1">
+      <c r="E22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="1">
         <v>3</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I22" s="1"/>
+      <c r="I22" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1</v>
       </c>
       <c r="C23" s="1">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1">
         <v>6</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>89</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>90</v>
@@ -1892,87 +1989,100 @@
       <c r="I23" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J23" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="K23" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B24" s="1"/>
+        <v>88</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1</v>
+      </c>
       <c r="C24" s="1">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1">
         <v>6</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="1">
+      <c r="E24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="1">
         <v>2</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I24" s="1"/>
+      <c r="I24" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" s="1"/>
+        <v>88</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
       <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1">
         <v>6</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="E25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" s="1">
         <v>3</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I25" s="1"/>
+      <c r="I25" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="1:11">
       <c r="B26" s="1"/>
-      <c r="D26" s="1"/>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="1:11">
       <c r="B27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="G27" s="1"/>
+      <c r="E27" s="1"/>
       <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:11">
       <c r="B28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="G28" s="1"/>
+      <c r="E28" s="1"/>
       <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:11">
       <c r="B29" s="1"/>
-      <c r="D29" s="1"/>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="1"/>
-      <c r="D30" s="1"/>
-    </row>
-    <row r="31" spans="1:10">
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="1"/>
-      <c r="D31" s="1"/>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="1"/>
-      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1"/>
@@ -2059,114 +2169,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="15.5" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="23.25" customWidth="1"/>
-    <col min="5" max="5" width="37.8796296296296" customWidth="1"/>
-    <col min="6" max="6" width="25.8796296296296" customWidth="1"/>
+    <col min="2" max="2" width="16.5" customWidth="1"/>
+    <col min="3" max="3" width="23.25" customWidth="1"/>
+    <col min="4" max="4" width="37.8796296296296" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E1" t="s">
         <v>103</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" t="s">
-        <v>110</v>
+      <c r="B2">
+        <v>46</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/OTA.xlsx
+++ b/OTA.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="112">
   <si>
     <t>BUS NAME</t>
   </si>
@@ -53,9 +53,6 @@
     <t>ECUindex</t>
   </si>
   <si>
-    <t>logical Address</t>
-  </si>
-  <si>
     <t>req CANID</t>
   </si>
   <si>
@@ -107,6 +104,9 @@
     <t>Infotainment CANFD</t>
   </si>
   <si>
+    <t>0x1D2</t>
+  </si>
+  <si>
     <t>Body Extend CAN</t>
   </si>
   <si>
@@ -134,9 +134,6 @@
     <t>0x77D</t>
   </si>
   <si>
-    <t>0x1D2</t>
-  </si>
-  <si>
     <t>Safety CANFD</t>
   </si>
   <si>
@@ -275,10 +272,7 @@
     <t>0x79A</t>
   </si>
   <si>
-    <t>0x331,0x313,0x181</t>
-  </si>
-  <si>
-    <t>100,100,20</t>
+    <t>0x313,0x181</t>
   </si>
   <si>
     <t>SAC</t>
@@ -299,6 +293,33 @@
     <t>0x797</t>
   </si>
   <si>
+    <t>0x331</t>
+  </si>
+  <si>
+    <t>BMS</t>
+  </si>
+  <si>
+    <t>0x713</t>
+  </si>
+  <si>
+    <t>0x793</t>
+  </si>
+  <si>
+    <t>0x107</t>
+  </si>
+  <si>
+    <t>CCU</t>
+  </si>
+  <si>
+    <t>0x73D</t>
+  </si>
+  <si>
+    <t>0x7BD</t>
+  </si>
+  <si>
+    <t>0x1D3</t>
+  </si>
+  <si>
     <t>Comfort Extended CAN</t>
   </si>
   <si>
@@ -311,10 +332,7 @@
     <t>0x6FB</t>
   </si>
   <si>
-    <t>0x2F2,0x2F3,0x2F4,0x1C2</t>
-  </si>
-  <si>
-    <t>100,100,100,20</t>
+    <t>0x2F2,0x1C2</t>
   </si>
   <si>
     <t>IDAM</t>
@@ -333,6 +351,9 @@
   </si>
   <si>
     <t>0x669</t>
+  </si>
+  <si>
+    <t>0x2F3,0x2F4</t>
   </si>
   <si>
     <t>Msg ID</t>
@@ -969,7 +990,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -980,6 +1001,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1293,7 +1317,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="21.7777777777778" customWidth="1"/>
@@ -1301,14 +1325,13 @@
     <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
     <col min="5" max="5" width="15.1111111111111" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="9" width="25.5555555555556" customWidth="1"/>
-    <col min="10" max="10" width="45.0925925925926" customWidth="1"/>
-    <col min="11" max="11" width="29.8055555555556" customWidth="1"/>
-    <col min="12" max="12" width="26.4074074074074" customWidth="1"/>
+    <col min="7" max="8" width="25.5555555555556" customWidth="1"/>
+    <col min="9" max="9" width="45.0925925925926" customWidth="1"/>
+    <col min="10" max="10" width="29.8055555555556" customWidth="1"/>
+    <col min="11" max="11" width="26.4074074074074" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1339,14 +1362,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="1"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -1358,12 +1378,14 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
@@ -1373,14 +1395,11 @@
       <c r="J2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="1"/>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
@@ -1392,25 +1411,24 @@
         <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1">
         <v>2</v>
       </c>
-      <c r="G3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1422,25 +1440,24 @@
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1">
         <v>3</v>
       </c>
-      <c r="G4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="H4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-    </row>
-    <row r="5" spans="1:12">
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
@@ -1453,12 +1470,15 @@
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="J5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="1">
+        <v>20</v>
+      </c>
       <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-    </row>
-    <row r="6" spans="1:12">
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -1477,22 +1497,21 @@
       <c r="F6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="H6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K6" s="1">
+      <c r="J6" s="1">
         <v>20</v>
       </c>
-      <c r="L6" s="1"/>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -1511,23 +1530,22 @@
       <c r="F7" s="1">
         <v>1</v>
       </c>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="K7" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
@@ -1539,28 +1557,27 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
@@ -1572,27 +1589,27 @@
         <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
@@ -1604,27 +1621,27 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>44</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K10" s="1">
+      <c r="J10" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:11">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
@@ -1636,21 +1653,21 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F11" s="1">
         <v>2</v>
       </c>
+      <c r="G11" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
@@ -1662,23 +1679,23 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F12" s="1">
         <v>3</v>
       </c>
+      <c r="G12" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="H12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="I12" s="1"/>
       <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:12">
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
@@ -1690,23 +1707,23 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F13" s="1">
         <v>4</v>
       </c>
+      <c r="G13" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="H13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:12">
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
@@ -1718,23 +1735,23 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F14" s="1">
         <v>5</v>
       </c>
+      <c r="G14" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="H14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:12">
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
@@ -1746,23 +1763,23 @@
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F15" s="1">
         <v>6</v>
       </c>
+      <c r="G15" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
@@ -1774,10 +1791,13 @@
         <v>5</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>63</v>
@@ -1788,13 +1808,10 @@
       <c r="J16" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
@@ -1806,23 +1823,23 @@
         <v>5</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F17" s="1">
         <v>2</v>
       </c>
+      <c r="G17" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="H17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I17" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11">
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
@@ -1834,23 +1851,23 @@
         <v>5</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F18" s="1">
         <v>3</v>
       </c>
+      <c r="G18" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="H18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11">
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
@@ -1862,23 +1879,23 @@
         <v>5</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F19" s="1">
         <v>4</v>
       </c>
+      <c r="G19" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="H19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
@@ -1890,10 +1907,13 @@
         <v>7</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>78</v>
@@ -1902,15 +1922,12 @@
         <v>79</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
@@ -1922,23 +1939,23 @@
         <v>7</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F21" s="1">
         <v>2</v>
       </c>
+      <c r="G21" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="H21" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>84</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11">
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
@@ -1950,83 +1967,91 @@
         <v>7</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F22" s="1">
         <v>3</v>
       </c>
+      <c r="G22" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="H22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1">
+        <v>7</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="2" t="s">
+      <c r="F23" s="1">
+        <v>4</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="1">
-        <v>1</v>
-      </c>
-      <c r="C23" s="1">
-        <v>2</v>
-      </c>
-      <c r="D23" s="1">
-        <v>6</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1">
+        <v>7</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="F24" s="1">
+        <v>5</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="H24" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1">
-        <v>2</v>
-      </c>
-      <c r="D24" s="1">
-        <v>6</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F24" s="1">
-        <v>2</v>
-      </c>
-      <c r="H24" s="1" t="s">
+      <c r="J24" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="B25" s="1">
         <v>1</v>
@@ -2038,10 +2063,13 @@
         <v>6</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="F25" s="1">
-        <v>3</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>98</v>
@@ -2049,78 +2077,133 @@
       <c r="I25" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="B26" s="1"/>
-      <c r="E26" s="1"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="B27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="J25" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2</v>
+      </c>
+      <c r="D26" s="1">
+        <v>6</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1">
+        <v>6</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="1">
+        <v>3</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J27" s="4">
+        <v>100100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="B28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="1:11">
+    </row>
+    <row r="29" spans="1:10">
       <c r="B29" s="1"/>
       <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="B30" s="1"/>
       <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="B31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:10">
       <c r="A32" s="1"/>
       <c r="E32" s="1"/>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1"/>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1"/>
-    </row>
-    <row r="38" spans="1:1">
+    <row r="33" spans="1:5">
+      <c r="A33" s="1"/>
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1"/>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:5">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:5">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:5">
       <c r="A41" s="1"/>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:5">
       <c r="A42" s="1"/>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:5">
       <c r="A43" s="1"/>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:5">
       <c r="A44" s="1"/>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:5">
       <c r="A45" s="1"/>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:5">
       <c r="A46" s="1"/>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:5">
       <c r="A47" s="1"/>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:5">
       <c r="A48" s="1"/>
     </row>
     <row r="49" spans="1:1">
@@ -2158,6 +2241,12 @@
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1"/>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1"/>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2179,21 +2268,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B2">
         <v>46</v>

--- a/OTA.xlsx
+++ b/OTA.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="113">
   <si>
     <t>BUS NAME</t>
   </si>
@@ -332,7 +332,7 @@
     <t>0x6FB</t>
   </si>
   <si>
-    <t>0x2F2,0x1C2</t>
+    <t>20</t>
   </si>
   <si>
     <t>IDAM</t>
@@ -353,7 +353,10 @@
     <t>0x669</t>
   </si>
   <si>
-    <t>0x2F3,0x2F4</t>
+    <t>0x2F2,0x2F3,0x2F4</t>
+  </si>
+  <si>
+    <t>100,100,100</t>
   </si>
   <si>
     <t>Msg ID</t>
@@ -990,7 +993,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1001,9 +1004,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2075,10 +2075,10 @@
         <v>98</v>
       </c>
       <c r="I25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2107,7 +2107,7 @@
         <v>102</v>
       </c>
       <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
+      <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
@@ -2137,8 +2137,8 @@
       <c r="I27" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="J27" s="4">
-        <v>100100</v>
+      <c r="J27" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2268,21 +2268,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2">
         <v>46</v>
